--- a/data/trans_bre/P2C_R1-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R1-Provincia-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 0,0</t>
+          <t>-4,24; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 7,44</t>
+          <t>-0,94; 7,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 2,94</t>
+          <t>-0,84; 3,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-25,32; 18,79</t>
+          <t>-24,74; 22,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-42,68; 962,49</t>
+          <t>-44,85; 1129,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-49,12; 86,14</t>
+          <t>-48,84; 104,7</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,46</t>
+          <t>0,33; 3,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 1,21</t>
+          <t>-0,6; 1,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 1,41</t>
+          <t>-1,68; 1,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-20,71; 3,25</t>
+          <t>-21,77; 3,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-62,35; 24,35</t>
+          <t>-65,65; 27,02</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,16</t>
+          <t>0,0; 3,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,71</t>
+          <t>0,0; 3,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 1,81</t>
+          <t>-1,28; 1,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,82; 17,73</t>
+          <t>-12,28; 17,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-33,31; 81,14</t>
+          <t>-29,63; 83,56</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 0,0</t>
+          <t>-2,12; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,71</t>
+          <t>0,63; 3,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,23</t>
+          <t>0,35; 3,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-22,11; 5,66</t>
+          <t>-23,07; 6,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-59,04; 39,64</t>
+          <t>-61,44; 41,3</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 2,48</t>
+          <t>-6,25; 1,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 0,0</t>
+          <t>-7,2; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,21; -0,76</t>
+          <t>-8,41; -0,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 21,43</t>
+          <t>-7,98; 21,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-29,67; 276,45</t>
+          <t>-32,89; 241,3</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,32</t>
+          <t>0,0; 4,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 0,0</t>
+          <t>-3,38; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 1,16</t>
+          <t>-3,67; 1,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,34; 13,53</t>
+          <t>-8,35; 13,23</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-31,02; 84,5</t>
+          <t>-30,41; 84,66</t>
         </is>
       </c>
     </row>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 0,45</t>
+          <t>-0,71; 0,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 1,56</t>
+          <t>-1,79; 1,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 1,09</t>
+          <t>-1,29; 1,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-24,87; 8,65</t>
+          <t>-21,8; 10,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-82,98; 343,39</t>
+          <t>-76,65; 353,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-95,02; 128,44</t>
+          <t>-94,37; 136,53</t>
         </is>
       </c>
     </row>
@@ -1360,27 +1360,27 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 1,33</t>
+          <t>-1,42; 1,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 0,76</t>
+          <t>-0,79; 0,71</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 1,96</t>
+          <t>-0,82; 2,05</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,96; 8,25</t>
+          <t>0,64; 8,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 820,61</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1390,12 +1390,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-57,58; 645,05</t>
+          <t>-65,75; 742,15</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,15; 388,09</t>
+          <t>3,36; 408,55</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,8</t>
+          <t>-0,39; 0,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,97</t>
+          <t>-0,25; 1,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 0,64</t>
+          <t>-0,59; 0,59</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-11,92; 1,72</t>
+          <t>-11,4; 2,5</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-43,24; 243,11</t>
+          <t>-49,16; 212,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-28,56; 187,9</t>
+          <t>-28,45; 193,1</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-50,52; 101,51</t>
+          <t>-48,05; 98,26</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-63,94; 10,82</t>
+          <t>-58,91; 17,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2C_R1-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R1-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,91</t>
+          <t>-0,2</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-5,29%</t>
+          <t>-0,61%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 0,0</t>
+          <t>-4,53; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 7,72</t>
+          <t>-0,62; 7,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 3,35</t>
+          <t>-1,26; 2,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-24,74; 22,01</t>
+          <t>-20,44; 20,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-44,85; 1129,97</t>
+          <t>-41,44; 892,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-48,84; 104,7</t>
+          <t>-47,85; 107,7</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-7,8</t>
+          <t>-7,17</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-33,31%</t>
+          <t>-32,09%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,44</t>
+          <t>0,51; 3,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 1,5</t>
+          <t>-0,59; 1,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 1,38</t>
+          <t>-1,59; 1,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-21,77; 3,96</t>
+          <t>-20,03; 2,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-65,65; 27,02</t>
+          <t>-62,65; 20,63</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,96</t>
+          <t>5,05</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>17,59%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,24</t>
+          <t>0,0; 3,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,48</t>
+          <t>0,0; 4,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 1,78</t>
+          <t>-1,29; 1,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 17,39</t>
+          <t>-11,07; 19,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-29,63; 83,56</t>
+          <t>-28,75; 92,5</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-6,51</t>
+          <t>-5,67</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-25,78%</t>
+          <t>-24,72%</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 0,0</t>
+          <t>-2,6; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,63</t>
+          <t>0,64; 3,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,29</t>
+          <t>0,34; 3,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-23,07; 6,12</t>
+          <t>-22,6; 6,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-61,44; 41,3</t>
+          <t>-62,29; 47,51</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,82</t>
+          <t>8,71</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>62,41%</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 1,82</t>
+          <t>-7,78; 1,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 0,0</t>
+          <t>-7,4; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,41; -0,77</t>
+          <t>-8,21; -0,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 21,17</t>
+          <t>-6,8; 21,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-32,89; 241,3</t>
+          <t>-33,07; 318,95</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,61</t>
+          <t>3,35</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>15,51%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,0</t>
+          <t>0,0; 4,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 0,0</t>
+          <t>-3,81; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 1,19</t>
+          <t>-3,75; 1,44</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 13,23</t>
+          <t>-7,49; 14,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-30,41; 84,66</t>
+          <t>-27,33; 100,07</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-6,0</t>
+          <t>8,21</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-57,95%</t>
+          <t>73,36%</t>
         </is>
       </c>
     </row>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,45</t>
+          <t>-0,71; 0,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 1,59</t>
+          <t>-1,96; 1,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 1,18</t>
+          <t>-1,37; 1,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-21,8; 10,33</t>
+          <t>-3,16; 19,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-76,65; 353,2</t>
+          <t>-87,44; 306,9</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-94,37; 136,53</t>
+          <t>-25,76; 333,87</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4,65</t>
+          <t>4,81</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>125,21%</t>
+          <t>135,96%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 1,39</t>
+          <t>-1,42; 1,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1370,17 +1370,17 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 2,05</t>
+          <t>-0,75; 1,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,64; 8,06</t>
+          <t>1,0; 8,11</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1390,12 +1390,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-65,75; 742,15</t>
+          <t>-62,03; 658,06</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,36; 408,55</t>
+          <t>14,1; 433,07</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-3,21</t>
+          <t>1,54</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-19,32%</t>
+          <t>10,15%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,73</t>
+          <t>-0,37; 0,72</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,0</t>
+          <t>-0,19; 1,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 0,59</t>
+          <t>-0,6; 0,61</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-11,4; 2,5</t>
+          <t>-2,38; 4,7</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-49,16; 212,0</t>
+          <t>-45,44; 216,68</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-28,45; 193,1</t>
+          <t>-20,16; 185,9</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-48,05; 98,26</t>
+          <t>-47,68; 98,53</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-58,91; 17,21</t>
+          <t>-13,23; 37,08</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2C_R1-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R1-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son remunerados</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados y estos son remunerados</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
